--- a/file/players_updated.xlsx
+++ b/file/players_updated.xlsx
@@ -61232,7 +61232,7 @@
         <v>Perfecto</v>
       </c>
       <c r="B823" t="str">
-        <v>no team</v>
+        <v>Bench</v>
       </c>
       <c r="C823" t="str">
         <v>dynamic</v>
@@ -61244,10 +61244,10 @@
         <v>0</v>
       </c>
       <c r="F823">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G823" t="str">
-        <v>none</v>
+        <v>BC.Game</v>
       </c>
       <c r="H823">
         <v>0</v>
@@ -62194,7 +62194,7 @@
         <v>kl1m</v>
       </c>
       <c r="B836" t="str">
-        <v>no team</v>
+        <v>Bench</v>
       </c>
       <c r="C836" t="str">
         <v>dynamic</v>
@@ -62206,10 +62206,10 @@
         <v>0</v>
       </c>
       <c r="F836">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G836" t="str">
-        <v>none</v>
+        <v>Envy</v>
       </c>
       <c r="H836">
         <v>0</v>
